--- a/data/trans_orig/IP25B_1_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP25B_1_R-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12216</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24339</t>
+          <t>24439</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17727</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41976</t>
+          <t>43143</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33783</t>
+          <t>33934</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62393</t>
+          <t>61888</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76939</t>
+          <t>76839</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89062</t>
+          <t>90184</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93220</t>
+          <t>92053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117469</t>
+          <t>118122</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174081</t>
+          <t>174586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>202691</t>
+          <t>202540</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11573</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23804</t>
+          <t>24286</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>10976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>24770</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26439</t>
+          <t>25770</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46185</t>
+          <t>43997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68866</t>
+          <t>68384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81097</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70663</t>
+          <t>70803</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83497</t>
+          <t>84597</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>142058</t>
+          <t>144246</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>161804</t>
+          <t>162473</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,31%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19834</t>
+          <t>18628</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10478</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23772</t>
+          <t>23929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>20910</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39322</t>
+          <t>38676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31358</t>
+          <t>32564</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43179</t>
+          <t>43627</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40081</t>
+          <t>39924</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53375</t>
+          <t>52826</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75723</t>
+          <t>76369</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93795</t>
+          <t>94135</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,82%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38944</t>
+          <t>39862</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120316</t>
+          <t>117970</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46878</t>
+          <t>47176</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77349</t>
+          <t>75607</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95044</t>
+          <t>97535</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>184614</t>
+          <t>197766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94211</t>
+          <t>96557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>175583</t>
+          <t>174665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138993</t>
+          <t>140735</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>169464</t>
+          <t>169166</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>246255</t>
+          <t>233103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>335825</t>
+          <t>333334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26155</t>
+          <t>26748</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45166</t>
+          <t>46853</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>34894</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73708</t>
+          <t>73355</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68367</t>
+          <t>68753</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112900</t>
+          <t>109239</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71359</t>
+          <t>69672</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90370</t>
+          <t>89777</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86030</t>
+          <t>86383</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123883</t>
+          <t>124844</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>163363</t>
+          <t>167024</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>207896</t>
+          <t>207510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>19470</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16621</t>
+          <t>17436</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32852</t>
+          <t>32994</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47143</t>
+          <t>47329</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58292</t>
+          <t>58535</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54992</t>
+          <t>54177</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65874</t>
+          <t>65870</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>105418</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>121888</t>
+          <t>122030</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,16%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131054</t>
+          <t>132512</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>229211</t>
+          <t>230320</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>155278</t>
+          <t>152194</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>213094</t>
+          <t>210953</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>301917</t>
+          <t>300047</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>408018</t>
+          <t>424401</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>413781</t>
+          <t>412672</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>511938</t>
+          <t>510480</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>529220</t>
+          <t>531361</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>587036</t>
+          <t>590120</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>977288</t>
+          <t>960905</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1083389</t>
+          <t>1085259</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,34%</t>
         </is>
       </c>
     </row>
